--- a/data_output/median_cscar.xlsx
+++ b/data_output/median_cscar.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -367,239 +367,183 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>bicarbonate</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>acetate</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>bicarbonate</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>formate</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>site</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BA1B</t>
+          <t>BA1B (Mildly Alkaline)</t>
         </is>
       </c>
       <c r="B2">
         <v>20</v>
       </c>
       <c r="C2">
-        <v>0.02753549657809758</v>
+        <v>0.07973017139197162</v>
       </c>
       <c r="D2">
-        <v>0.0413331948414237</v>
+        <v>0.03202714868788992</v>
       </c>
       <c r="E2">
-        <v>0.0005448915511457709</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>BA1B-20m</t>
-        </is>
+        <v>0.0005622942278966118</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BA1B</t>
+          <t>BA1B (Mildly Alkaline)</t>
         </is>
       </c>
       <c r="B3">
         <v>150</v>
       </c>
       <c r="C3">
-        <v>0.01542202968012782</v>
+        <v>0.008971431473007057</v>
       </c>
       <c r="D3">
-        <v>0.008299530826970103</v>
+        <v>0.01784589425304618</v>
       </c>
       <c r="E3">
-        <v>0.001064125857078232</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>BA1B-150m</t>
-        </is>
+        <v>0.001209028971841391</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BA1B</t>
+          <t>BA1B (Mildly Alkaline)</t>
         </is>
       </c>
       <c r="B4">
         <v>250</v>
       </c>
       <c r="C4">
-        <v>0.006460214238584351</v>
+        <v>0.2892707566590473</v>
       </c>
       <c r="D4">
-        <v>0.103303731372731</v>
+        <v>0.006930192383762541</v>
       </c>
       <c r="E4">
-        <v>0.001022805746534746</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>BA1B-250m</t>
-        </is>
+        <v>0.001053057480387823</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BA4A</t>
+          <t>BA4A (Moderately Alkaline)</t>
         </is>
       </c>
       <c r="B5">
         <v>20</v>
       </c>
       <c r="C5">
-        <v>0.02484906511255947</v>
+        <v>0.1450547989150799</v>
       </c>
       <c r="D5">
-        <v>0.06806664795097457</v>
+        <v>0.03358651800066281</v>
       </c>
       <c r="E5">
-        <v>0.001235449885152485</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>BA4A-20m</t>
-        </is>
+        <v>0.001292717966653217</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BA4A</t>
+          <t>BA4A (Moderately Alkaline)</t>
         </is>
       </c>
       <c r="B6">
         <v>150</v>
       </c>
       <c r="C6">
-        <v>0.02057800120171194</v>
+        <v>0.3100372154747512</v>
       </c>
       <c r="D6">
-        <v>0.07798478925823979</v>
+        <v>0.02885949783531774</v>
       </c>
       <c r="E6">
-        <v>0.0003814895396422725</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>BA4A-150m</t>
-        </is>
+        <v>0.0004053494057092727</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BA4A</t>
+          <t>BA4A (Moderately Alkaline)</t>
         </is>
       </c>
       <c r="B7">
         <v>270</v>
       </c>
       <c r="C7">
-        <v>0.02410471118620635</v>
+        <v>0.1905268957202816</v>
       </c>
       <c r="D7">
-        <v>0.07979760553513618</v>
+        <v>0.03324739631736683</v>
       </c>
       <c r="E7">
-        <v>0.0002576174640429658</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>BA4A-270m</t>
-        </is>
+        <v>0.0002956215692049217</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BA3A</t>
+          <t>BA3A (Hyperalkaline)</t>
         </is>
       </c>
       <c r="B8">
         <v>20</v>
       </c>
       <c r="C8">
-        <v>0.001773030122184529</v>
+        <v>0.00330289824180115</v>
       </c>
       <c r="D8">
-        <v>0.001851379250790631</v>
+        <v>0.00249428620027406</v>
       </c>
       <c r="E8">
-        <v>0.0002854842086151311</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>BA3A-20m</t>
-        </is>
+        <v>0.0004306093000884713</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BA3A</t>
+          <t>BA3A (Hyperalkaline)</t>
         </is>
       </c>
       <c r="B9">
         <v>150</v>
       </c>
       <c r="C9">
-        <v>0.0002217420291454735</v>
+        <v>0.001161804149553292</v>
       </c>
       <c r="D9">
-        <v>0.001013734629403324</v>
+        <v>0.0003130106210985206</v>
       </c>
       <c r="E9">
-        <v>9.070332786507971e-05</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>BA3A-150m</t>
-        </is>
+        <v>9.480303102480731e-05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BA3A</t>
+          <t>BA3A (Hyperalkaline)</t>
         </is>
       </c>
       <c r="B10">
         <v>270</v>
       </c>
       <c r="C10">
-        <v>3.20591872064304e-05</v>
-      </c>
-      <c r="D10">
-        <v>3.447185855203546e-05</v>
-      </c>
-      <c r="E10">
-        <v>1.398207499681232e-05</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>BA3A-270m</t>
-        </is>
+        <v>4.607576373360642e-05</v>
       </c>
     </row>
   </sheetData>

--- a/data_output/median_cscar.xlsx
+++ b/data_output/median_cscar.xlsx
@@ -530,7 +530,7 @@
         <v>0.0003130106210985206</v>
       </c>
       <c r="E9">
-        <v>9.480303102480731e-05</v>
+        <v>9.480303102480731E-05</v>
       </c>
     </row>
     <row r="10">
@@ -543,7 +543,7 @@
         <v>270</v>
       </c>
       <c r="C10">
-        <v>4.607576373360642e-05</v>
+        <v>4.607576373360642E-05</v>
       </c>
     </row>
   </sheetData>
